--- a/public/exports/29188505.xlsx
+++ b/public/exports/29188505.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558842</t>
+          <t xml:space="preserve">311558846</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">

--- a/public/exports/29188505.xlsx
+++ b/public/exports/29188505.xlsx
@@ -14689,7 +14689,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558846</t>
+          <t xml:space="preserve">311558842</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558830</t>
+          <t xml:space="preserve">311558842</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -22339,12 +22339,12 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876582</t>
+          <t xml:space="preserve">311876603</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M298" t="inlineStr">

--- a/public/exports/29188505.xlsx
+++ b/public/exports/29188505.xlsx
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558842</t>
+          <t xml:space="preserve">311558830</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -22339,12 +22339,12 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876603</t>
+          <t xml:space="preserve">311876582</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
